--- a/data/odds/Brown Munde 2026 Betting Odds.xlsx
+++ b/data/odds/Brown Munde 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
   <si>
     <t>Record</t>
   </si>
@@ -36,196 +36,214 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
+    <t>Team BB</t>
+  </si>
+  <si>
+    <t>NoHalfSends</t>
+  </si>
+  <si>
+    <t>The Man In Jahmyrror</t>
+  </si>
+  <si>
     <t>Team Padodara</t>
   </si>
   <si>
-    <t>NoHalfSends</t>
-  </si>
-  <si>
-    <t>The Man In Jahmyrror</t>
-  </si>
-  <si>
-    <t>Team BB</t>
-  </si>
-  <si>
     <t>THE BIGMADBLUE</t>
   </si>
   <si>
     <t>Still Rollin'</t>
   </si>
   <si>
+    <t>Hark</t>
+  </si>
+  <si>
     <t>Bhals</t>
   </si>
   <si>
-    <t>Hark</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>97.3%</t>
-  </si>
-  <si>
-    <t>89.7%</t>
-  </si>
-  <si>
-    <t>87.9%</t>
-  </si>
-  <si>
-    <t>85.6%</t>
-  </si>
-  <si>
-    <t>83.5%</t>
-  </si>
-  <si>
-    <t>53.4%</t>
-  </si>
-  <si>
-    <t>50.6%</t>
-  </si>
-  <si>
-    <t>24.4%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>-3604</t>
-  </si>
-  <si>
-    <t>-871</t>
-  </si>
-  <si>
-    <t>-726</t>
-  </si>
-  <si>
-    <t>-594</t>
-  </si>
-  <si>
-    <t>-506</t>
-  </si>
-  <si>
-    <t>-115</t>
-  </si>
-  <si>
-    <t>-102</t>
-  </si>
-  <si>
-    <t>+310</t>
-  </si>
-  <si>
-    <t>+3025</t>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>96.5%</t>
+  </si>
+  <si>
+    <t>94.9%</t>
+  </si>
+  <si>
+    <t>94.2%</t>
+  </si>
+  <si>
+    <t>77.9%</t>
+  </si>
+  <si>
+    <t>64.4%</t>
+  </si>
+  <si>
+    <t>64.0%</t>
+  </si>
+  <si>
+    <t>52.6%</t>
+  </si>
+  <si>
+    <t>22.1%</t>
+  </si>
+  <si>
+    <t>17.4%</t>
+  </si>
+  <si>
+    <t>16.0%</t>
+  </si>
+  <si>
+    <t>-2757</t>
+  </si>
+  <si>
+    <t>-1861</t>
+  </si>
+  <si>
+    <t>-1624</t>
+  </si>
+  <si>
+    <t>-352</t>
+  </si>
+  <si>
+    <t>-181</t>
+  </si>
+  <si>
+    <t>-178</t>
+  </si>
+  <si>
+    <t>-111</t>
+  </si>
+  <si>
+    <t>+352</t>
+  </si>
+  <si>
+    <t>+475</t>
+  </si>
+  <si>
+    <t>+525</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>43.4%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
-    <t>13.3%</t>
-  </si>
-  <si>
-    <t>7.3%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+    <t>39.6%</t>
+  </si>
+  <si>
+    <t>24.5%</t>
+  </si>
+  <si>
+    <t>22.9%</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
   </si>
   <si>
     <t>2.0%</t>
   </si>
   <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>+130</t>
-  </si>
-  <si>
-    <t>+513</t>
-  </si>
-  <si>
-    <t>+599</t>
-  </si>
-  <si>
-    <t>+652</t>
-  </si>
-  <si>
-    <t>+1270</t>
-  </si>
-  <si>
-    <t>+3746</t>
+    <t>+153</t>
+  </si>
+  <si>
+    <t>+308</t>
+  </si>
+  <si>
+    <t>+337</t>
+  </si>
+  <si>
+    <t>+1654</t>
+  </si>
+  <si>
+    <t>+3348</t>
   </si>
   <si>
     <t>+4900</t>
   </si>
   <si>
-    <t>+14186</t>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>51.0%</t>
-  </si>
-  <si>
-    <t>19.7%</t>
-  </si>
-  <si>
-    <t>17.2%</t>
-  </si>
-  <si>
-    <t>5.6%</t>
-  </si>
-  <si>
-    <t>4.7%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-104</t>
-  </si>
-  <si>
-    <t>+408</t>
-  </si>
-  <si>
-    <t>+481</t>
-  </si>
-  <si>
-    <t>+1686</t>
-  </si>
-  <si>
-    <t>+2028</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>33.7%</t>
+  </si>
+  <si>
+    <t>29.1%</t>
+  </si>
+  <si>
+    <t>21.5%</t>
+  </si>
+  <si>
+    <t>4.9%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>+197</t>
+  </si>
+  <si>
+    <t>+244</t>
+  </si>
+  <si>
+    <t>+365</t>
+  </si>
+  <si>
+    <t>+1941</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+2678</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -611,7 +629,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -625,7 +643,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -633,13 +651,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -653,7 +671,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -667,7 +685,7 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -681,7 +699,7 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -689,13 +707,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -703,13 +721,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -720,10 +738,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -731,13 +749,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -772,38 +790,38 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -814,38 +832,38 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -853,13 +871,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -870,10 +888,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -881,13 +899,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -895,13 +913,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -933,13 +951,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -950,10 +968,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -961,97 +979,97 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1062,10 +1080,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Brown Munde 2026 Betting Odds.xlsx
+++ b/data/odds/Brown Munde 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>Record</t>
   </si>
@@ -30,220 +30,190 @@
     <t>Team</t>
   </si>
   <si>
+    <t>BurgerBoyz</t>
+  </si>
+  <si>
+    <t>Team BB</t>
+  </si>
+  <si>
     <t>Banta’s Bunties</t>
   </si>
   <si>
-    <t>BurgerBoyz</t>
-  </si>
-  <si>
-    <t>Team BB</t>
+    <t>THE BIGMADBLUE</t>
+  </si>
+  <si>
+    <t>The Man In Jahmyrror</t>
+  </si>
+  <si>
+    <t>Team Padodara</t>
   </si>
   <si>
     <t>NoHalfSends</t>
   </si>
   <si>
-    <t>The Man In Jahmyrror</t>
-  </si>
-  <si>
-    <t>Team Padodara</t>
-  </si>
-  <si>
-    <t>THE BIGMADBLUE</t>
-  </si>
-  <si>
     <t>Still Rollin'</t>
   </si>
   <si>
+    <t>Bhals</t>
+  </si>
+  <si>
     <t>Hark</t>
   </si>
   <si>
-    <t>Bhals</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>96.5%</t>
-  </si>
-  <si>
-    <t>94.9%</t>
-  </si>
-  <si>
-    <t>94.2%</t>
-  </si>
-  <si>
-    <t>77.9%</t>
-  </si>
-  <si>
-    <t>64.4%</t>
-  </si>
-  <si>
-    <t>64.0%</t>
-  </si>
-  <si>
-    <t>52.6%</t>
-  </si>
-  <si>
-    <t>22.1%</t>
-  </si>
-  <si>
-    <t>17.4%</t>
-  </si>
-  <si>
-    <t>16.0%</t>
-  </si>
-  <si>
-    <t>-2757</t>
-  </si>
-  <si>
-    <t>-1861</t>
-  </si>
-  <si>
-    <t>-1624</t>
-  </si>
-  <si>
-    <t>-352</t>
-  </si>
-  <si>
-    <t>-181</t>
-  </si>
-  <si>
-    <t>-178</t>
-  </si>
-  <si>
-    <t>-111</t>
-  </si>
-  <si>
-    <t>+352</t>
-  </si>
-  <si>
-    <t>+475</t>
-  </si>
-  <si>
-    <t>+525</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>98.9%</t>
+  </si>
+  <si>
+    <t>96.6%</t>
+  </si>
+  <si>
+    <t>96.3%</t>
+  </si>
+  <si>
+    <t>93.3%</t>
+  </si>
+  <si>
+    <t>90.7%</t>
+  </si>
+  <si>
+    <t>58.1%</t>
+  </si>
+  <si>
+    <t>35.9%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>-8991</t>
+  </si>
+  <si>
+    <t>-2841</t>
+  </si>
+  <si>
+    <t>-2603</t>
+  </si>
+  <si>
+    <t>-1393</t>
+  </si>
+  <si>
+    <t>-975</t>
+  </si>
+  <si>
+    <t>-139</t>
+  </si>
+  <si>
+    <t>+179</t>
+  </si>
+  <si>
+    <t>+462</t>
+  </si>
+  <si>
+    <t>+1393</t>
+  </si>
+  <si>
+    <t>+1654</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
+    <t>36.1%</t>
+  </si>
+  <si>
+    <t>21.3%</t>
+  </si>
+  <si>
+    <t>19.0%</t>
+  </si>
+  <si>
+    <t>14.3%</t>
+  </si>
+  <si>
+    <t>7.6%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>+177</t>
+  </si>
+  <si>
+    <t>+369</t>
+  </si>
+  <si>
+    <t>+426</t>
+  </si>
+  <si>
+    <t>+599</t>
+  </si>
+  <si>
+    <t>+1216</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
     <t>39.6%</t>
   </si>
   <si>
-    <t>24.5%</t>
-  </si>
-  <si>
-    <t>22.9%</t>
-  </si>
-  <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
+    <t>36.5%</t>
+  </si>
+  <si>
+    <t>13.7%</t>
+  </si>
+  <si>
+    <t>6.9%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
   </si>
   <si>
     <t>+153</t>
   </si>
   <si>
-    <t>+308</t>
-  </si>
-  <si>
-    <t>+337</t>
-  </si>
-  <si>
-    <t>+1654</t>
-  </si>
-  <si>
-    <t>+3348</t>
-  </si>
-  <si>
-    <t>+4900</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>33.7%</t>
-  </si>
-  <si>
-    <t>29.1%</t>
-  </si>
-  <si>
-    <t>21.5%</t>
-  </si>
-  <si>
-    <t>4.9%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>+197</t>
-  </si>
-  <si>
-    <t>+244</t>
-  </si>
-  <si>
-    <t>+365</t>
-  </si>
-  <si>
-    <t>+1941</t>
-  </si>
-  <si>
-    <t>+2173</t>
-  </si>
-  <si>
-    <t>+2678</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>+174</t>
+  </si>
+  <si>
+    <t>+630</t>
+  </si>
+  <si>
+    <t>+1349</t>
+  </si>
+  <si>
+    <t>+3126</t>
   </si>
 </sst>
 </file>
@@ -626,10 +596,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -640,10 +610,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -654,10 +624,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -665,13 +635,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -679,13 +649,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -693,13 +663,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -707,13 +677,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -724,10 +694,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -735,13 +705,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -749,13 +719,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -776,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -790,7 +760,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -798,13 +768,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>49</v>
@@ -812,13 +782,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
@@ -829,10 +799,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -840,13 +810,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>52</v>
@@ -854,13 +824,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>53</v>
@@ -871,10 +841,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -882,13 +852,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>55</v>
@@ -896,30 +866,30 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -951,13 +921,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -965,13 +935,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -982,10 +952,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -993,13 +963,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1007,13 +977,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1021,55 +991,55 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1083,7 +1053,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Brown Munde 2026 Betting Odds.xlsx
+++ b/data/odds/Brown Munde 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
   <si>
     <t>Record</t>
   </si>
@@ -36,184 +36,193 @@
     <t>Team BB</t>
   </si>
   <si>
+    <t>Team Padodara</t>
+  </si>
+  <si>
+    <t>THE BIGMADBLUE</t>
+  </si>
+  <si>
+    <t>The Man In Jahmyrror</t>
+  </si>
+  <si>
     <t>Banta’s Bunties</t>
   </si>
   <si>
-    <t>THE BIGMADBLUE</t>
-  </si>
-  <si>
-    <t>The Man In Jahmyrror</t>
-  </si>
-  <si>
-    <t>Team Padodara</t>
+    <t>Still Rollin'</t>
+  </si>
+  <si>
+    <t>Bhals</t>
+  </si>
+  <si>
+    <t>Hark</t>
   </si>
   <si>
     <t>NoHalfSends</t>
   </si>
   <si>
-    <t>Still Rollin'</t>
-  </si>
-  <si>
-    <t>Bhals</t>
-  </si>
-  <si>
-    <t>Hark</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>98.9%</t>
-  </si>
-  <si>
-    <t>96.6%</t>
-  </si>
-  <si>
-    <t>96.3%</t>
-  </si>
-  <si>
-    <t>93.3%</t>
-  </si>
-  <si>
-    <t>90.7%</t>
-  </si>
-  <si>
-    <t>58.1%</t>
-  </si>
-  <si>
-    <t>35.9%</t>
-  </si>
-  <si>
-    <t>17.8%</t>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>97.0%</t>
+  </si>
+  <si>
+    <t>89.0%</t>
+  </si>
+  <si>
+    <t>79.9%</t>
+  </si>
+  <si>
+    <t>77.5%</t>
+  </si>
+  <si>
+    <t>70.5%</t>
+  </si>
+  <si>
+    <t>41.0%</t>
+  </si>
+  <si>
+    <t>22.3%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-3233</t>
+  </si>
+  <si>
+    <t>-809</t>
+  </si>
+  <si>
+    <t>-398</t>
+  </si>
+  <si>
+    <t>-344</t>
+  </si>
+  <si>
+    <t>-239</t>
+  </si>
+  <si>
+    <t>+144</t>
+  </si>
+  <si>
+    <t>+348</t>
+  </si>
+  <si>
+    <t>+521</t>
+  </si>
+  <si>
+    <t>+1371</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>74.3%</t>
+  </si>
+  <si>
+    <t>14.5%</t>
+  </si>
+  <si>
+    <t>6.2%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-289</t>
+  </si>
+  <si>
+    <t>+590</t>
+  </si>
+  <si>
+    <t>+1513</t>
+  </si>
+  <si>
+    <t>+5163</t>
+  </si>
+  <si>
+    <t>+7592</t>
+  </si>
+  <si>
+    <t>+8991</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>47.8%</t>
+  </si>
+  <si>
+    <t>22.6%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
   </si>
   <si>
     <t>6.7%</t>
   </si>
   <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>-8991</t>
-  </si>
-  <si>
-    <t>-2841</t>
-  </si>
-  <si>
-    <t>-2603</t>
-  </si>
-  <si>
-    <t>-1393</t>
-  </si>
-  <si>
-    <t>-975</t>
-  </si>
-  <si>
-    <t>-139</t>
-  </si>
-  <si>
-    <t>+179</t>
-  </si>
-  <si>
-    <t>+462</t>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>+109</t>
+  </si>
+  <si>
+    <t>+342</t>
+  </si>
+  <si>
+    <t>+421</t>
   </si>
   <si>
     <t>+1393</t>
   </si>
   <si>
-    <t>+1654</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>36.1%</t>
-  </si>
-  <si>
-    <t>21.3%</t>
-  </si>
-  <si>
-    <t>19.0%</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
-    <t>7.6%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+177</t>
-  </si>
-  <si>
-    <t>+369</t>
-  </si>
-  <si>
-    <t>+426</t>
-  </si>
-  <si>
-    <t>+599</t>
-  </si>
-  <si>
-    <t>+1216</t>
-  </si>
-  <si>
-    <t>+7043</t>
+    <t>+5456</t>
   </si>
   <si>
     <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>39.6%</t>
-  </si>
-  <si>
-    <t>36.5%</t>
-  </si>
-  <si>
-    <t>13.7%</t>
-  </si>
-  <si>
-    <t>6.9%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>+153</t>
-  </si>
-  <si>
-    <t>+174</t>
-  </si>
-  <si>
-    <t>+630</t>
-  </si>
-  <si>
-    <t>+1349</t>
-  </si>
-  <si>
-    <t>+3126</t>
   </si>
 </sst>
 </file>
@@ -596,10 +605,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,10 +619,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -624,10 +633,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -635,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -652,10 +661,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -663,13 +672,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -680,10 +689,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -694,10 +703,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,13 +714,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -719,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -760,38 +769,38 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -799,13 +808,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -816,10 +825,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -827,13 +836,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -844,10 +853,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -858,10 +867,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -869,13 +878,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -883,13 +892,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -921,13 +930,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -935,13 +944,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -952,10 +961,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -966,10 +975,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -977,13 +986,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -994,18 +1003,18 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -1016,30 +1025,30 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1050,10 +1059,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Brown Munde 2026 Betting Odds.xlsx
+++ b/data/odds/Brown Munde 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -36,193 +36,190 @@
     <t>Team BB</t>
   </si>
   <si>
+    <t>THE BIGMADBLUE</t>
+  </si>
+  <si>
+    <t>Banta’s Bunties</t>
+  </si>
+  <si>
     <t>Team Padodara</t>
   </si>
   <si>
-    <t>THE BIGMADBLUE</t>
+    <t>Still Rollin'</t>
   </si>
   <si>
     <t>The Man In Jahmyrror</t>
   </si>
   <si>
-    <t>Banta’s Bunties</t>
-  </si>
-  <si>
-    <t>Still Rollin'</t>
-  </si>
-  <si>
     <t>Bhals</t>
   </si>
   <si>
+    <t>NoHalfSends</t>
+  </si>
+  <si>
     <t>Hark</t>
   </si>
   <si>
-    <t>NoHalfSends</t>
-  </si>
-  <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>97.0%</t>
-  </si>
-  <si>
-    <t>89.0%</t>
-  </si>
-  <si>
-    <t>79.9%</t>
-  </si>
-  <si>
-    <t>77.5%</t>
-  </si>
-  <si>
-    <t>70.5%</t>
-  </si>
-  <si>
-    <t>41.0%</t>
-  </si>
-  <si>
-    <t>22.3%</t>
-  </si>
-  <si>
-    <t>16.1%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>96.2%</t>
+  </si>
+  <si>
+    <t>94.2%</t>
+  </si>
+  <si>
+    <t>91.1%</t>
+  </si>
+  <si>
+    <t>78.4%</t>
+  </si>
+  <si>
+    <t>71.6%</t>
+  </si>
+  <si>
+    <t>49.6%</t>
+  </si>
+  <si>
+    <t>11.7%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-3233</t>
-  </si>
-  <si>
-    <t>-809</t>
-  </si>
-  <si>
-    <t>-398</t>
-  </si>
-  <si>
-    <t>-344</t>
-  </si>
-  <si>
-    <t>-239</t>
-  </si>
-  <si>
-    <t>+144</t>
-  </si>
-  <si>
-    <t>+348</t>
-  </si>
-  <si>
-    <t>+521</t>
-  </si>
-  <si>
-    <t>+1371</t>
+    <t>-2532</t>
+  </si>
+  <si>
+    <t>-1624</t>
+  </si>
+  <si>
+    <t>-1024</t>
+  </si>
+  <si>
+    <t>-363</t>
+  </si>
+  <si>
+    <t>-252</t>
+  </si>
+  <si>
+    <t>+102</t>
+  </si>
+  <si>
+    <t>+755</t>
+  </si>
+  <si>
+    <t>+2400</t>
+  </si>
+  <si>
+    <t>+3025</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>74.3%</t>
-  </si>
-  <si>
-    <t>14.5%</t>
-  </si>
-  <si>
-    <t>6.2%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
+    <t>80.7%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>5.9%</t>
+  </si>
+  <si>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-418</t>
+  </si>
+  <si>
+    <t>+1182</t>
+  </si>
+  <si>
+    <t>+1595</t>
+  </si>
+  <si>
+    <t>+2841</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>44.6%</t>
+  </si>
+  <si>
+    <t>35.7%</t>
+  </si>
+  <si>
+    <t>16.8%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-289</t>
-  </si>
-  <si>
-    <t>+590</t>
-  </si>
-  <si>
-    <t>+1513</t>
-  </si>
-  <si>
-    <t>+5163</t>
-  </si>
-  <si>
-    <t>+7592</t>
-  </si>
-  <si>
-    <t>+8991</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>47.8%</t>
-  </si>
-  <si>
-    <t>22.6%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>+109</t>
-  </si>
-  <si>
-    <t>+342</t>
-  </si>
-  <si>
-    <t>+421</t>
-  </si>
-  <si>
-    <t>+1393</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>+124</t>
+  </si>
+  <si>
+    <t>+180</t>
+  </si>
+  <si>
+    <t>+495</t>
+  </si>
+  <si>
+    <t>+4248</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -605,10 +602,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -619,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -633,10 +630,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -647,10 +644,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,13 +655,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,10 +672,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -686,13 +683,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,13 +697,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,13 +711,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,13 +725,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -755,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -769,7 +766,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
         <v>49</v>
@@ -783,7 +780,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -797,7 +794,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -811,7 +808,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
         <v>52</v>
@@ -822,10 +819,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -839,7 +836,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
         <v>54</v>
@@ -850,10 +847,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>55</v>
@@ -861,13 +858,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -878,7 +875,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>
@@ -889,7 +886,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
@@ -919,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -930,7 +927,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>57</v>
@@ -944,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
@@ -958,7 +955,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>59</v>
@@ -972,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>60</v>
@@ -1000,13 +997,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1017,32 +1014,32 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>48</v>

--- a/data/odds/Brown Munde 2026 Betting Odds.xlsx
+++ b/data/odds/Brown Munde 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Record</t>
   </si>
@@ -33,24 +33,24 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
+    <t>Banta’s Bunties</t>
+  </si>
+  <si>
+    <t>THE BIGMADBLUE</t>
+  </si>
+  <si>
+    <t>Still Rollin'</t>
+  </si>
+  <si>
     <t>Team BB</t>
   </si>
   <si>
-    <t>THE BIGMADBLUE</t>
-  </si>
-  <si>
-    <t>Banta’s Bunties</t>
+    <t>The Man In Jahmyrror</t>
   </si>
   <si>
     <t>Team Padodara</t>
   </si>
   <si>
-    <t>Still Rollin'</t>
-  </si>
-  <si>
-    <t>The Man In Jahmyrror</t>
-  </si>
-  <si>
     <t>Bhals</t>
   </si>
   <si>
@@ -60,166 +60,151 @@
     <t>Hark</t>
   </si>
   <si>
-    <t>6-0</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
+    <t>7-0</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>96.2%</t>
-  </si>
-  <si>
-    <t>94.2%</t>
-  </si>
-  <si>
-    <t>91.1%</t>
-  </si>
-  <si>
-    <t>78.4%</t>
-  </si>
-  <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>49.6%</t>
-  </si>
-  <si>
-    <t>11.7%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
+    <t>97.4%</t>
+  </si>
+  <si>
+    <t>95.0%</t>
+  </si>
+  <si>
+    <t>90.4%</t>
+  </si>
+  <si>
+    <t>88.1%</t>
+  </si>
+  <si>
+    <t>69.1%</t>
+  </si>
+  <si>
+    <t>50.3%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-2532</t>
-  </si>
-  <si>
-    <t>-1624</t>
-  </si>
-  <si>
-    <t>-1024</t>
-  </si>
-  <si>
-    <t>-363</t>
-  </si>
-  <si>
-    <t>-252</t>
-  </si>
-  <si>
-    <t>+102</t>
-  </si>
-  <si>
-    <t>+755</t>
-  </si>
-  <si>
-    <t>+2400</t>
-  </si>
-  <si>
-    <t>+3025</t>
+    <t>-3746</t>
+  </si>
+  <si>
+    <t>-1900</t>
+  </si>
+  <si>
+    <t>-942</t>
+  </si>
+  <si>
+    <t>-740</t>
+  </si>
+  <si>
+    <t>-224</t>
+  </si>
+  <si>
+    <t>-101</t>
+  </si>
+  <si>
+    <t>+1233</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>80.7%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>87.7%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-713</t>
+  </si>
+  <si>
+    <t>+1438</t>
+  </si>
+  <si>
+    <t>+3126</t>
+  </si>
+  <si>
+    <t>+6150</t>
+  </si>
+  <si>
+    <t>+8991</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>49.2%</t>
+  </si>
+  <si>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-418</t>
-  </si>
-  <si>
-    <t>+1182</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+2841</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>+103</t>
+  </si>
+  <si>
+    <t>+152</t>
+  </si>
+  <si>
+    <t>+900</t>
+  </si>
+  <si>
+    <t>+11011</t>
   </si>
   <si>
     <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>44.6%</t>
-  </si>
-  <si>
-    <t>35.7%</t>
-  </si>
-  <si>
-    <t>16.8%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+124</t>
-  </si>
-  <si>
-    <t>+180</t>
-  </si>
-  <si>
-    <t>+495</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -641,7 +626,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -655,7 +640,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -669,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -769,7 +754,7 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -783,7 +768,7 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -797,7 +782,7 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -805,13 +790,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -819,83 +804,83 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -930,10 +915,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -944,10 +929,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -958,10 +943,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -972,10 +957,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -983,69 +968,69 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1056,10 +1041,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Brown Munde 2026 Betting Odds.xlsx
+++ b/data/odds/Brown Munde 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Record</t>
   </si>
@@ -39,12 +39,12 @@
     <t>THE BIGMADBLUE</t>
   </si>
   <si>
+    <t>Team BB</t>
+  </si>
+  <si>
     <t>Still Rollin'</t>
   </si>
   <si>
-    <t>Team BB</t>
-  </si>
-  <si>
     <t>The Man In Jahmyrror</t>
   </si>
   <si>
@@ -81,130 +81,127 @@
     <t>100.0%</t>
   </si>
   <si>
-    <t>97.4%</t>
-  </si>
-  <si>
-    <t>95.0%</t>
-  </si>
-  <si>
-    <t>90.4%</t>
-  </si>
-  <si>
-    <t>88.1%</t>
-  </si>
-  <si>
-    <t>69.1%</t>
-  </si>
-  <si>
-    <t>50.3%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
+    <t>97.8%</t>
+  </si>
+  <si>
+    <t>95.4%</t>
+  </si>
+  <si>
+    <t>90.3%</t>
+  </si>
+  <si>
+    <t>89.3%</t>
+  </si>
+  <si>
+    <t>67.1%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-4445</t>
+  </si>
+  <si>
+    <t>-2074</t>
+  </si>
+  <si>
+    <t>-931</t>
+  </si>
+  <si>
+    <t>-835</t>
+  </si>
+  <si>
+    <t>-204</t>
+  </si>
+  <si>
+    <t>-100</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+12400</t>
+  </si>
+  <si>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>88.0%</t>
+  </si>
+  <si>
+    <t>6.1%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
   </si>
   <si>
     <t>1.4%</t>
   </si>
   <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-3746</t>
-  </si>
-  <si>
-    <t>-1900</t>
-  </si>
-  <si>
-    <t>-942</t>
-  </si>
-  <si>
-    <t>-740</t>
-  </si>
-  <si>
-    <t>-224</t>
-  </si>
-  <si>
-    <t>-101</t>
-  </si>
-  <si>
-    <t>+1233</t>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-733</t>
+  </si>
+  <si>
+    <t>+1539</t>
+  </si>
+  <si>
+    <t>+2757</t>
   </si>
   <si>
     <t>+7043</t>
   </si>
   <si>
-    <t>+12400</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>87.7%</t>
-  </si>
-  <si>
-    <t>6.5%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-713</t>
-  </si>
-  <si>
-    <t>+1438</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+6150</t>
-  </si>
-  <si>
-    <t>+8991</t>
+    <t>+11011</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>49.2%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>+103</t>
-  </si>
-  <si>
-    <t>+152</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>48.5%</t>
+  </si>
+  <si>
+    <t>39.4%</t>
+  </si>
+  <si>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>+106</t>
+  </si>
+  <si>
+    <t>+154</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -754,7 +751,7 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -768,7 +765,7 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -782,12 +779,12 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -796,12 +793,12 @@
         <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -810,35 +807,35 @@
         <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -849,10 +846,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -863,10 +860,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -877,10 +874,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -915,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -929,7 +926,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -943,7 +940,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -957,10 +954,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -974,35 +971,35 @@
         <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1013,10 +1010,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1027,10 +1024,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1041,10 +1038,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
